--- a/simulations/correction_peat_market/AS_marché/AS_marché_hobby/inv/AS_pos_inv_mark_VF2.xlsx
+++ b/simulations/correction_peat_market/AS_marché/AS_marché_hobby/inv/AS_pos_inv_mark_VF2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\hravoaha\Desktop\Thèse\Thèse 2023\Objectif 2\biowaste_optim\simulations\correction_peat_market\AS_marché\AS_marché_hobby\inv\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57A4F56C-BBFC-4D16-B104-F09F948A1F7D}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ABAD8073-DC88-4040-BB45-5201C3147366}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="8980" windowHeight="4840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -280,10 +280,10 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -588,53 +588,53 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:51" x14ac:dyDescent="0.35">
       <c r="A1" s="2"/>
       <c r="B1" s="5"/>
-      <c r="C1" s="6"/>
+      <c r="C1" s="7"/>
       <c r="D1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="7"/>
-      <c r="F1" s="7"/>
-      <c r="G1" s="7"/>
-      <c r="H1" s="7"/>
-      <c r="I1" s="7"/>
-      <c r="J1" s="7"/>
-      <c r="K1" s="7"/>
-      <c r="L1" s="7"/>
-      <c r="M1" s="7"/>
-      <c r="N1" s="7"/>
-      <c r="O1" s="7"/>
-      <c r="P1" s="7"/>
-      <c r="Q1" s="7"/>
-      <c r="R1" s="7"/>
-      <c r="S1" s="7"/>
-      <c r="T1" s="7"/>
-      <c r="U1" s="7"/>
-      <c r="V1" s="7"/>
-      <c r="W1" s="7"/>
-      <c r="X1" s="7"/>
-      <c r="Y1" s="6"/>
+      <c r="E1" s="6"/>
+      <c r="F1" s="6"/>
+      <c r="G1" s="6"/>
+      <c r="H1" s="6"/>
+      <c r="I1" s="6"/>
+      <c r="J1" s="6"/>
+      <c r="K1" s="6"/>
+      <c r="L1" s="6"/>
+      <c r="M1" s="6"/>
+      <c r="N1" s="6"/>
+      <c r="O1" s="6"/>
+      <c r="P1" s="6"/>
+      <c r="Q1" s="6"/>
+      <c r="R1" s="6"/>
+      <c r="S1" s="6"/>
+      <c r="T1" s="6"/>
+      <c r="U1" s="6"/>
+      <c r="V1" s="6"/>
+      <c r="W1" s="6"/>
+      <c r="X1" s="6"/>
+      <c r="Y1" s="7"/>
       <c r="Z1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="AA1" s="7"/>
-      <c r="AB1" s="6"/>
+      <c r="AA1" s="6"/>
+      <c r="AB1" s="7"/>
       <c r="AC1" s="2" t="s">
         <v>2</v>
       </c>
       <c r="AD1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="AE1" s="6"/>
+      <c r="AE1" s="7"/>
       <c r="AF1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="AG1" s="6"/>
+      <c r="AG1" s="7"/>
       <c r="AH1" s="2" t="s">
         <v>5</v>
       </c>
@@ -644,11 +644,11 @@
       <c r="AJ1" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="AK1" s="7"/>
-      <c r="AL1" s="7"/>
-      <c r="AM1" s="7"/>
-      <c r="AN1" s="7"/>
-      <c r="AO1" s="6"/>
+      <c r="AK1" s="6"/>
+      <c r="AL1" s="6"/>
+      <c r="AM1" s="6"/>
+      <c r="AN1" s="6"/>
+      <c r="AO1" s="7"/>
     </row>
     <row r="2" spans="1:51" x14ac:dyDescent="0.35">
       <c r="A2" s="2"/>
@@ -1279,6 +1279,11 @@
       <c r="AY9">
         <f t="shared" si="5"/>
         <v>98.71</v>
+      </c>
+    </row>
+    <row r="11" spans="1:51" x14ac:dyDescent="0.35">
+      <c r="AK11" s="4">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
